--- a/docs/result/row-data/3rd-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
+++ b/docs/result/row-data/3rd-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/row-data/3rd-test/pessimistic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7800AA-74E5-A24A-95F4-4D7799831DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9823A468-6A16-4B42-8230-261339DFEE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{E183A82D-E7BE-C048-8629-DC2E35FE4921}"/>
   </bookViews>
@@ -4789,6 +4789,1476 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="738151" cy="355097"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F50AAF-C806-F54D-896C-27C120761632}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="3200400"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F50AAF-C806-F54D-896C-27C120761632}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="3200400"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑛_𝑖−1) </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1599284" cy="182871"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB817FA9-51D6-994D-AE36-0C7463A76762}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="4114800"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑤𝑖𝑡h𝑖𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB817FA9-51D6-994D-AE36-0C7463A76762}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="4114800"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑤𝑖𝑡ℎ𝑖𝑛=Σ_(𝑖=1)^2 (𝑛_𝑖−1) 𝜎_𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="964816" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9107A206-2CD8-004B-89BC-D18194CD7FF9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="4572000"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9107A206-2CD8-004B-89BC-D18194CD7FF9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="4572000"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1984902" cy="186782"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66563638-59C2-C144-AB91-74E0272B397E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="5486400"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑏𝑒𝑡𝑤𝑒𝑒𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66563638-59C2-C144-AB91-74E0272B397E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="5486400"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑏𝑒𝑡𝑤𝑒𝑒𝑛=Σ_(𝑖=1)^𝑘 𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1842235" cy="500137"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB7C941-3D83-6743-ADCB-073BC61AF204}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="5943600"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>total</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:rad>
+                      <m:radPr>
+                        <m:degHide m:val="on"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:radPr>
+                      <m:deg/>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>within</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>between</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <m:rPr>
+                                <m:sty m:val="p"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>N</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−1</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:rad>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB7C941-3D83-6743-ADCB-073BC61AF204}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="5943600"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>total=√((SS_within+SS_between)/(N−1))</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="438710" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DADFEFC4-8D1F-E84C-BAB3-72D9A4E2BD07}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="6629400"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>2</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DADFEFC4-8D1F-E84C-BAB3-72D9A4E2BD07}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4089400" y="6629400"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2𝜎_𝑡𝑜𝑡𝑎𝑙</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5115,7 +6585,7 @@
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -5393,98 +6863,156 @@
         <f>A10*B10</f>
         <v>184754.079</v>
       </c>
+      <c r="E15">
+        <f>(A10-1)*POWER(C10,2)</f>
+        <v>43419764.049248002</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
       <c r="B16">
         <f>A11*B11</f>
         <v>150040.935</v>
       </c>
+      <c r="E16">
+        <f>(A11-1)*POWER(C11,2)</f>
+        <v>25940929.763435997</v>
+      </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:5">
       <c r="B17">
         <f>A12*B12</f>
         <v>97.006</v>
       </c>
+      <c r="E17">
+        <f>(A12-1)*POWER(C12,2)</f>
+        <v>52.887757000000001</v>
+      </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:5">
       <c r="B18">
         <f>A13*B13</f>
         <v>23</v>
       </c>
+      <c r="E18">
+        <f>(A13-1)*POWER(C13,2)</f>
+        <v>2.25</v>
+      </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:5">
       <c r="B19">
         <f>SUM(B15:B18)</f>
         <v>334915.01999999996</v>
       </c>
+      <c r="E19">
+        <f>SUM(E15:E18)</f>
+        <v>69360748.950441003</v>
+      </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:5">
       <c r="B20">
         <f>SUM(A10:A13)</f>
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:5">
       <c r="B21">
         <f>B19/B20</f>
         <v>669.83003999999994</v>
       </c>
+      <c r="E21">
+        <f>A10*POWER((B10-B$21),2)</f>
+        <v>16238.428118726051</v>
+      </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:5">
       <c r="B22">
         <f>ROUND(B21,2)</f>
         <v>669.83</v>
       </c>
+      <c r="E22">
+        <f>A11*POWER((B11-B$21),2)</f>
+        <v>789977.53738253051</v>
+      </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="23" spans="2:5">
+      <c r="E23">
+        <f>A12*POWER((B12-B$21),2)</f>
+        <v>6152129.0436631413</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
       <c r="B24">
         <f>POWER(C10,2)</f>
         <v>156186.20161600001</v>
       </c>
+      <c r="E24">
+        <f>A13*POWER((B13-B$21),2)</f>
+        <v>866796.88313280302</v>
+      </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:5">
       <c r="B25">
         <f>POWER(C11,2)</f>
         <v>127161.42040899998</v>
       </c>
+      <c r="E25">
+        <f>SUM(E21:E24)</f>
+        <v>7825141.8922972009</v>
+      </c>
     </row>
-    <row r="26" spans="2:2">
+    <row r="26" spans="2:5">
       <c r="B26">
         <f>POWER(C12,2)</f>
         <v>4.068289</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:5">
       <c r="B27">
         <f>POWER(C13,2)</f>
         <v>2.25</v>
       </c>
+      <c r="E27">
+        <f>SQRT((E19+E25)/(B20-1))</f>
+        <v>393.29523766939161</v>
+      </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:5">
       <c r="B28">
         <f>POWER(B10,2)</f>
         <v>438510.16440100002</v>
       </c>
+      <c r="E28">
+        <f>ROUND(E27,2)</f>
+        <v>393.3</v>
+      </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="2:5">
       <c r="B29">
         <f>POWER(B11,2)</f>
         <v>535687.85664900008</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:5">
       <c r="B30">
         <f>POWER(B12,2)</f>
         <v>48.011041000000006</v>
       </c>
+      <c r="E30">
+        <f>2*E27</f>
+        <v>786.59047533878322</v>
+      </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:5">
       <c r="B31">
         <f>POWER(B13,2)</f>
         <v>132.25</v>
       </c>
+      <c r="E31">
+        <f>ROUND(E30,2)</f>
+        <v>786.59</v>
+      </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:5">
       <c r="B32">
         <f>B24+B28</f>
         <v>594696.36601700005</v>
